--- a/교재/엑셀교재v2/028-029_피벗테이블_실습.xlsx
+++ b/교재/엑셀교재v2/028-029_피벗테이블_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC06CAE6-3EFD-424B-8E5B-B7EDE20FC14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4B77A2-48E7-4D29-BB36-847A4CA93620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -29,24 +29,11 @@
     <pivotCache cacheId="0" r:id="rId7"/>
     <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="98">
   <si>
     <t>028 029 피벗 테이블 사용 안내</t>
   </si>
@@ -307,13 +294,46 @@
   </si>
   <si>
     <t>75-100</t>
+  </si>
+  <si>
+    <t>▶ 피벗 테이블 보고서는 동일 시트의 [B23] 셀에서 시작하시오.</t>
+  </si>
+  <si>
+    <t>▶ 피벗 테이블 옵션에서 빈 셀은 ‘**’ 기호로 표시, ‘레이블이 있는 셀 병합 및 가운데 맞춤’을 설정하고 행의 총합계가 나타나지 않도록 지정하시오.</t>
+  </si>
+  <si>
+    <t>▶ 입고량과 판매수량은 ‘표시 형식’ → ‘숫자’ 형태로 나타내시오.</t>
+  </si>
+  <si>
+    <t>▶ 보고서 레이아웃을 ‘개요 형식’으로 표시하시오.</t>
+  </si>
+  <si>
+    <t>▶ ‘공기청정기’와 ‘에어컨’ 제품만 표시하시오.</t>
+  </si>
+  <si>
+    <t>▶ ‘서울’ 지역의 ‘에어컨’ 제품의 입고량 데이터를 별도의 시트에 표시하고 시트 이름을 ‘★서울자료’로 표시하시오.</t>
+  </si>
+  <si>
+    <t>‘12월 제품 판매현황’을 이용하여 판매수량은 ‘행’, 제품명은 ‘열’로 처리하고</t>
+  </si>
+  <si>
+    <t>‘∑ 값’에 ‘입고량’의 최대 함수를 계산하는 피벗 테이블을 작성하시오.</t>
+  </si>
+  <si>
+    <t>▶ 피벗 테이블 보고서는 동일 시트의 [B21] 셀에서 시작하시오.</t>
+  </si>
+  <si>
+    <t>▶ 보고서 레이아웃을 ‘테이블 형식’으로 표시하시오.</t>
+  </si>
+  <si>
+    <t>▶ ‘판매수량’ 값에 그룹을 설정하시오. (시작: 0, 끝: 100, 단위: 25)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -346,6 +366,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -380,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -405,6 +431,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -425,8 +454,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -436,167 +465,76 @@
   <dxfs count="32">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </font>
     </dxf>
     <dxf>
       <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -684,73 +622,164 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+        <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1277,45 +1306,45 @@
     <dataField name="평균 : 판매수량" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="31">
+    <format dxfId="22">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="20">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="19">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="18">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="17">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="16">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -1328,7 +1357,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -1341,7 +1370,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -1427,25 +1456,25 @@
     <dataField name="최대 : 입고량" fld="3" subtotal="max" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="19">
+    <format dxfId="9">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="7">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="6">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="5">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="4">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="5" count="4">
@@ -1457,17 +1486,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1484,16 +1513,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DBB699F-3337-4E4D-BA79-C323578850D6}" name="표1" displayName="표1" ref="A1:G3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DBB699F-3337-4E4D-BA79-C323578850D6}" name="표1" displayName="표1" ref="A1:G3" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:G3" xr:uid="{2DBB699F-3337-4E4D-BA79-C323578850D6}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9E2D3121-C505-4B39-A7B5-A97968CABFFB}" name="제품명" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{4262AF64-01C8-4877-A126-87217BF87C2B}" name="지역" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{96D4E890-7D7B-43A4-AA6D-34E236FA69BA}" name="담당자" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{B6DFF5D7-33BD-471E-90F7-E48C2AFC4761}" name="입고량" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{05EBA15B-7E06-4969-A19A-E3740D60C5BD}" name="판매단가" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{37C8F07A-D9B8-4681-A04A-5F8280901359}" name="판매수량" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{A3F7D930-68DF-4425-AAB9-712AE3C016C2}" name="매출액" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E2D3121-C505-4B39-A7B5-A97968CABFFB}" name="제품명" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{4262AF64-01C8-4877-A126-87217BF87C2B}" name="지역" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{96D4E890-7D7B-43A4-AA6D-34E236FA69BA}" name="담당자" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B6DFF5D7-33BD-471E-90F7-E48C2AFC4761}" name="입고량" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{05EBA15B-7E06-4969-A19A-E3740D60C5BD}" name="판매단가" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{37C8F07A-D9B8-4681-A04A-5F8280901359}" name="판매수량" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{A3F7D930-68DF-4425-AAB9-712AE3C016C2}" name="매출액" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1704,12 +1733,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" ht="38.1" customHeight="1">
       <c r="A2" s="1"/>
@@ -1718,164 +1747,164 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
     </row>
     <row r="4" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
     </row>
     <row r="6" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
     </row>
     <row r="8" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
     </row>
     <row r="9" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
     </row>
     <row r="11" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
     </row>
     <row r="12" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
     </row>
     <row r="13" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
     </row>
     <row r="16" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="18" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
     </row>
     <row r="21" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
     </row>
     <row r="22" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -1912,7 +1941,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1920,26 +1949,22 @@
     <col min="3" max="4" width="17" customWidth="1"/>
     <col min="5" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
-    <col min="10" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1949,11 +1974,8 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -1977,13 +1999,11 @@
         <v>28</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="27" customHeight="1">
+      <c r="J3" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>30</v>
@@ -2008,11 +2028,11 @@
         <v>113600000</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="33" customHeight="1">
+      <c r="J4" s="21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="33" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -2037,13 +2057,11 @@
         <v>67200000</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="1:12" ht="33" customHeight="1">
+      <c r="J5" s="21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="33" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>33</v>
@@ -2068,13 +2086,9 @@
         <v>48060000</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-    </row>
-    <row r="7" spans="1:12" ht="33" customHeight="1">
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" ht="33" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>30</v>
@@ -2099,13 +2113,11 @@
         <v>109500000</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" ht="33" customHeight="1">
+      <c r="J7" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="33" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>43</v>
@@ -2130,13 +2142,9 @@
         <v>60000000</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1">
+      <c r="J8" s="21"/>
+    </row>
+    <row r="9" spans="1:10" ht="33" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -2161,13 +2169,11 @@
         <v>73720000</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:12" ht="33" customHeight="1">
+      <c r="J9" s="21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="33" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
@@ -2192,13 +2198,9 @@
         <v>64680000</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" ht="33" customHeight="1">
+      <c r="J10" s="21"/>
+    </row>
+    <row r="11" spans="1:10" ht="33" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>30</v>
@@ -2223,13 +2225,11 @@
         <v>63020000</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="33" customHeight="1">
+      <c r="J11" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="33" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>30</v>
@@ -2254,13 +2254,8 @@
         <v>85400000</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:12" ht="33" customHeight="1">
+    </row>
+    <row r="13" spans="1:10" ht="33" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>33</v>
@@ -2285,13 +2280,8 @@
         <v>27300000</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>33</v>
@@ -2316,11 +2306,8 @@
         <v>75000000</v>
       </c>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>30</v>
@@ -2345,11 +2332,8 @@
         <v>118320000</v>
       </c>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>33</v>
@@ -2374,13 +2358,8 @@
         <v>61740000</v>
       </c>
       <c r="I16" s="2"/>
-      <c r="J16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="17" spans="1:9" ht="27" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>30</v>
@@ -2405,11 +2384,8 @@
         <v>136000000</v>
       </c>
       <c r="I17" s="2"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-    </row>
-    <row r="18" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="18" spans="1:9" ht="27" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>43</v>
@@ -2434,11 +2410,8 @@
         <v>54000000</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-    </row>
-    <row r="19" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="19" spans="1:9" ht="27" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2448,11 +2421,8 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="20" spans="1:9" ht="27" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2462,11 +2432,8 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="21" spans="1:9" ht="27" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2476,11 +2443,8 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="22" spans="1:9" ht="27" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2490,11 +2454,8 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="23" spans="1:9" ht="27" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2504,11 +2465,8 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="24" spans="1:9" ht="27" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2518,11 +2476,8 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="25" spans="1:9" ht="27" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2532,11 +2487,8 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="26" spans="1:9" ht="27" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2546,11 +2498,8 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="27" spans="1:9" ht="27" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2560,11 +2509,8 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="28" spans="1:9" ht="27" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2574,11 +2520,8 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="29" spans="1:9" ht="27" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2588,11 +2531,8 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="30" spans="1:9" ht="27" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2602,11 +2542,8 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="31" spans="1:9" ht="27" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2616,11 +2553,8 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="32" spans="1:9" ht="27" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2630,11 +2564,8 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="33" spans="1:9" ht="27" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2644,11 +2575,8 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="34" spans="1:9" ht="27" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2658,11 +2586,8 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="35" spans="1:9" ht="27" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2672,11 +2597,8 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="36" spans="1:9" ht="27" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2686,11 +2608,8 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="37" spans="1:9" ht="27" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2700,11 +2619,8 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="38" spans="1:9" ht="27" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2714,11 +2630,8 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="39" spans="1:9" ht="27" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2728,11 +2641,8 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="40" spans="1:9" ht="27" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2742,24 +2652,10 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J16:L18"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J12:L12"/>
+  <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2879,15 +2775,15 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -2931,11 +2827,11 @@
         <v>28</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:12" ht="27" customHeight="1">
       <c r="A4" s="2"/>
@@ -2991,11 +2887,11 @@
         <v>67200000</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1">
       <c r="A6" s="2"/>
@@ -3022,11 +2918,11 @@
         <v>48060000</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="1:12" ht="33" customHeight="1">
       <c r="A7" s="2"/>
@@ -3053,11 +2949,11 @@
         <v>109500000</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1">
       <c r="A8" s="2"/>
@@ -3084,11 +2980,11 @@
         <v>60000000</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1">
       <c r="A9" s="2"/>
@@ -3115,11 +3011,11 @@
         <v>73720000</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="1:12" ht="33" customHeight="1">
       <c r="A10" s="2"/>
@@ -3146,11 +3042,11 @@
         <v>64680000</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:12" ht="33" customHeight="1">
       <c r="A11" s="2"/>
@@ -3177,11 +3073,11 @@
         <v>63020000</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="1:12" ht="33" customHeight="1">
       <c r="A12" s="2"/>
@@ -3208,11 +3104,11 @@
         <v>85400000</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="1:12" ht="33" customHeight="1">
       <c r="A13" s="2"/>
@@ -3239,11 +3135,11 @@
         <v>27300000</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="1:12" ht="27" customHeight="1">
       <c r="A14" s="2"/>
@@ -3328,11 +3224,11 @@
         <v>61740000</v>
       </c>
       <c r="I16" s="2"/>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="1:12" ht="27" customHeight="1">
       <c r="A17" s="2"/>
@@ -3359,9 +3255,9 @@
         <v>136000000</v>
       </c>
       <c r="I17" s="2"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="1:12" ht="27" customHeight="1">
       <c r="A18" s="2"/>
@@ -3388,9 +3284,9 @@
         <v>54000000</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="1:12" ht="27" customHeight="1">
       <c r="A19" s="2"/>
@@ -3473,14 +3369,14 @@
     <row r="24" spans="1:12" ht="27" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="20"/>
+      <c r="E24" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="19"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -3517,16 +3413,16 @@
       <c r="B26" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="12">
         <v>78</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="12">
         <v>54</v>
       </c>
       <c r="G26" s="5"/>
@@ -3541,16 +3437,16 @@
       <c r="B27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="12">
         <v>99</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="12">
         <v>75</v>
       </c>
       <c r="G27" s="5"/>
@@ -3565,16 +3461,16 @@
       <c r="B28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="12">
         <v>110</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="12">
         <v>49</v>
       </c>
       <c r="G28" s="5"/>
@@ -3589,16 +3485,16 @@
       <c r="B29" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="12">
         <v>160</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="12">
         <v>79</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="12" t="s">
         <v>81</v>
       </c>
       <c r="G29" s="5"/>
@@ -3613,16 +3509,16 @@
       <c r="B30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="12">
         <v>98</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="12">
         <v>64.5</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="12">
         <v>110</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="12">
         <v>66</v>
       </c>
       <c r="G30" s="5"/>
@@ -3637,16 +3533,16 @@
       <c r="B31" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="12">
         <v>170</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="12">
         <v>58.5</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="12" t="s">
         <v>81</v>
       </c>
       <c r="G31" s="5"/>
@@ -3661,16 +3557,16 @@
       <c r="B32" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="12">
         <v>428</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="12">
         <v>67.333333333333329</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="12">
         <v>397</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="12">
         <v>59.833333333333336</v>
       </c>
       <c r="G32" s="5"/>
@@ -3820,7 +3716,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3828,26 +3724,22 @@
     <col min="3" max="4" width="17" customWidth="1"/>
     <col min="5" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
-    <col min="10" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3857,11 +3749,8 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -3885,13 +3774,11 @@
         <v>28</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="27" customHeight="1">
+      <c r="J3" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>30</v>
@@ -3916,11 +3803,11 @@
         <v>113600000</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="33" customHeight="1">
+      <c r="J4" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="33" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -3945,13 +3832,9 @@
         <v>186200000</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="1:12" ht="33" customHeight="1">
+      <c r="J5" s="21"/>
+    </row>
+    <row r="6" spans="1:10" ht="33" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>43</v>
@@ -3976,13 +3859,11 @@
         <v>54000000</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-    </row>
-    <row r="7" spans="1:12" ht="33" customHeight="1">
+      <c r="J6" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="33" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>33</v>
@@ -4007,13 +3888,11 @@
         <v>11700000</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" ht="33" customHeight="1">
+      <c r="J7" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="33" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>30</v>
@@ -4038,13 +3917,11 @@
         <v>85400000</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1">
+      <c r="J8" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="33" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -4069,13 +3946,8 @@
         <v>61740000</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:12" ht="33" customHeight="1">
+    </row>
+    <row r="10" spans="1:10" ht="33" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
@@ -4100,13 +3972,8 @@
         <v>64680000</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" ht="33" customHeight="1">
+    </row>
+    <row r="11" spans="1:10" ht="33" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>30</v>
@@ -4131,13 +3998,8 @@
         <v>136000000</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="33" customHeight="1">
+    </row>
+    <row r="12" spans="1:10" ht="33" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>33</v>
@@ -4162,13 +4024,8 @@
         <v>75000000</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:12" ht="33" customHeight="1">
+    </row>
+    <row r="13" spans="1:10" ht="33" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>43</v>
@@ -4193,13 +4050,8 @@
         <v>60000000</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>30</v>
@@ -4224,11 +4076,8 @@
         <v>17400000</v>
       </c>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>33</v>
@@ -4253,11 +4102,8 @@
         <v>67200000</v>
       </c>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>30</v>
@@ -4282,13 +4128,8 @@
         <v>63020000</v>
       </c>
       <c r="I16" s="2"/>
-      <c r="J16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="17" spans="1:9" ht="27" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -4313,11 +4154,8 @@
         <v>48060000</v>
       </c>
       <c r="I17" s="2"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-    </row>
-    <row r="18" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="18" spans="1:9" ht="27" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>30</v>
@@ -4342,11 +4180,8 @@
         <v>109500000</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-    </row>
-    <row r="19" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="19" spans="1:9" ht="27" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4356,11 +4191,8 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="20" spans="1:9" ht="27" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4370,11 +4202,8 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="21" spans="1:9" ht="27" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4384,11 +4213,8 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="22" spans="1:9" ht="27" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4398,11 +4224,8 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="23" spans="1:9" ht="27" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4412,11 +4235,8 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="24" spans="1:9" ht="27" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4426,11 +4246,8 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="25" spans="1:9" ht="27" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4440,11 +4257,8 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="26" spans="1:9" ht="27" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4454,11 +4268,8 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="27" spans="1:9" ht="27" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -4468,11 +4279,8 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="28" spans="1:9" ht="27" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -4482,11 +4290,8 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="29" spans="1:9" ht="27" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -4496,11 +4301,8 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="30" spans="1:9" ht="27" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4510,11 +4312,8 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="31" spans="1:9" ht="27" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -4524,11 +4323,8 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="32" spans="1:9" ht="27" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -4538,11 +4334,8 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="33" spans="1:9" ht="27" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -4552,11 +4345,8 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="34" spans="1:9" ht="27" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -4566,11 +4356,8 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="35" spans="1:9" ht="27" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4580,11 +4367,8 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="36" spans="1:9" ht="27" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4594,11 +4378,8 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="37" spans="1:9" ht="27" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4608,11 +4389,8 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="38" spans="1:9" ht="27" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4622,11 +4400,8 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="39" spans="1:9" ht="27" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4636,11 +4411,8 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" ht="27" customHeight="1">
+    </row>
+    <row r="40" spans="1:9" ht="27" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4650,24 +4422,10 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J16:L18"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J12:L12"/>
+  <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4694,15 +4452,15 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -4746,11 +4504,11 @@
         <v>28</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:12" ht="27" customHeight="1">
       <c r="A4" s="2"/>
@@ -4806,11 +4564,11 @@
         <v>186200000</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1">
       <c r="A6" s="2"/>
@@ -4837,11 +4595,11 @@
         <v>54000000</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="1:12" ht="33" customHeight="1">
       <c r="A7" s="2"/>
@@ -4868,11 +4626,11 @@
         <v>11700000</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1">
       <c r="A8" s="2"/>
@@ -4899,11 +4657,11 @@
         <v>85400000</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1">
       <c r="A9" s="2"/>
@@ -4930,11 +4688,11 @@
         <v>61740000</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="1:12" ht="33" customHeight="1">
       <c r="A10" s="2"/>
@@ -4961,11 +4719,11 @@
         <v>64680000</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:12" ht="33" customHeight="1">
       <c r="A11" s="2"/>
@@ -4992,11 +4750,11 @@
         <v>136000000</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="1:12" ht="33" customHeight="1">
       <c r="A12" s="2"/>
@@ -5023,11 +4781,11 @@
         <v>75000000</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="1:12" ht="33" customHeight="1">
       <c r="A13" s="2"/>
@@ -5054,11 +4812,11 @@
         <v>60000000</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="1:12" ht="27" customHeight="1">
       <c r="A14" s="2"/>
@@ -5143,11 +4901,11 @@
         <v>63020000</v>
       </c>
       <c r="I16" s="2"/>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="1:12" ht="27" customHeight="1">
       <c r="A17" s="2"/>
@@ -5174,9 +4932,9 @@
         <v>48060000</v>
       </c>
       <c r="I17" s="2"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="1:12" ht="27" customHeight="1">
       <c r="A18" s="2"/>
@@ -5203,9 +4961,9 @@
         <v>109500000</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="1:12" ht="27" customHeight="1">
       <c r="A19" s="2"/>
